--- a/output/full_scan/batch_seq7_2026-08-31.xlsx
+++ b/output/full_scan/batch_seq7_2026-08-31.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1108.341747094733</v>
+        <v>1398.341747094733</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>399.5</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>68.99494407179138</v>
+        <v>68.99494411376031</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25.39314592271674</v>
+        <v>25.39314607920112</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.643106225135554</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.107362300133593</v>
+        <v>1.107362299561236</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6532</v>
+        <v>6670</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>997.2433959921028</v>
+        <v>1167.403172125947</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>95.3</v>
+        <v>287.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>68.84709273065988</v>
+        <v>67.33811571883378</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>34.55031377108611</v>
+        <v>20.51722147308711</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.431264920225618</v>
+        <v>2.582559594662106</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.8501646463319465</v>
+        <v>1.951130135143262</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6670</v>
+        <v>6532</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>877.4031721259469</v>
+        <v>1137.243395992103</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>287.5</v>
+        <v>95.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.33811555921562</v>
+        <v>68.8470928761169</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>20.51722137858088</v>
+        <v>34.550313771886</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.582559594662106</v>
+        <v>2.431264920225618</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,11 +676,11 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.951130136765008</v>
+        <v>0.8501646455115313</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>788.1012187545156</v>
+        <v>978.1012187545156</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>254.5</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>76.95563000432561</v>
+        <v>76.95563001077498</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>29.73617557427988</v>
+        <v>29.7361756988048</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2.410121875451562</v>
@@ -729,11 +729,11 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>5.050182406463124</v>
+        <v>5.050182405699943</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>766.4431841312835</v>
+        <v>966.4431841312852</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1140</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>61.08226174593154</v>
+        <v>61.08226180726786</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18.79776770226164</v>
+        <v>18.7977676942158</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2.169549879950917</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>15.42691076846966</v>
+        <v>15.42691076751569</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6761</v>
+        <v>6727</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>758.1215198253823</v>
+        <v>936.8280630494236</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>189</v>
+        <v>524</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,29 +817,29 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>61.86280793430452</v>
+        <v>65.83494857889772</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>21.59610869599293</v>
+        <v>25.97126974490805</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.4570522480428802</v>
+        <v>1.598924459125505</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.628810781243942</v>
+        <v>12.43330229239596</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>736.4994738007281</v>
+        <v>936.499473800728</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>194</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>65.79990333031532</v>
+        <v>65.7999033346606</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>16.17290021868605</v>
+        <v>16.17290021311524</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>3.902481062704565</v>
@@ -888,11 +888,11 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2.00449682214353</v>
+        <v>2.00449682220079</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>682.277677551287</v>
+        <v>927.2776775512868</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>7095</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>70.16586066301022</v>
+        <v>70.16586070137396</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>30.68308338144783</v>
+        <v>30.68308340201916</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.204946778701299</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>54.25203852454842</v>
+        <v>54.25203851787074</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6716</v>
+        <v>6761</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>679.3824405282188</v>
+        <v>873.1215198253822</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.47495617162305</v>
+        <v>61.86280796416292</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>33.78707929594304</v>
+        <v>21.59610870046352</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.6200735099120146</v>
+        <v>0.4570522480428802</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.276966954266598</v>
+        <v>1.628810781034041</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6588</v>
+        <v>6739</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>675.606066662688</v>
+        <v>857.1526694348235</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>110.5</v>
+        <v>1180</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>61.68615942747365</v>
+        <v>62.54564799128209</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>25.64484282228999</v>
+        <v>11.63709051443089</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8606066662688049</v>
+        <v>1.702388256880734</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1.650379684714331</v>
+        <v>24.00275167855166</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6739</v>
+        <v>6829</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>657.1526694348244</v>
+        <v>854.3495262605743</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1180</v>
+        <v>245</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>62.54564797910206</v>
+        <v>63.35733626918467</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>11.63709050283721</v>
+        <v>18.36492779380383</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.702388256880734</v>
+        <v>1.268784972293685</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>1</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>24.00275168150896</v>
+        <v>3.411223161456757</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6829</v>
+        <v>6588</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>654.3495262605744</v>
+        <v>845.606066662688</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>245</v>
+        <v>110.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.35733629641005</v>
+        <v>61.6861594536163</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>18.36492772004381</v>
+        <v>25.64484284234411</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.268784972293685</v>
+        <v>0.8606066662688049</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>3.411223162124511</v>
+        <v>1.650379684733418</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6538</v>
+        <v>6805</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>630.008002341396</v>
+        <v>790.8140762964887</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>205.5</v>
+        <v>2305</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.03096450707646</v>
+        <v>70.30689672112838</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>37.40443922644343</v>
+        <v>29.77933824840611</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.01065182970435</v>
+        <v>1.197836172094355</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.555474042428354</v>
+        <v>53.08625697780308</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6727</v>
+        <v>6538</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>621.8280630494236</v>
+        <v>770.008002341396</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>524</v>
+        <v>205.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>65.83494857410697</v>
+        <v>65.03096451794691</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>25.97126971266411</v>
+        <v>37.40443925315965</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.598924459125505</v>
+        <v>1.01065182970435</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,11 +1259,11 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>12.43330229251043</v>
+        <v>1.555474042237552</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>615.2831475598127</v>
+        <v>755.2831475598125</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>629</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.53773062322206</v>
+        <v>57.53773059399209</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>27.54753748434276</v>
+        <v>27.54753754327008</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>3.449106752781125</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>11.27305324058322</v>
+        <v>11.27305324210952</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6666</v>
+        <v>6668</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>580.4996245241246</v>
+        <v>727.4095889967907</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>44.4</v>
+        <v>44</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>55.65789158254415</v>
+        <v>70.97259469641156</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>18.99948345003758</v>
+        <v>26.79695094009622</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.3652480252165466</v>
+        <v>2.712796945948098</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1462973657029882</v>
+        <v>1.052824725346456</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6771</v>
+        <v>6651</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>579.9751171828688</v>
+        <v>719.1863984270725</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>41.75</v>
+        <v>148.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>56.88001466125824</v>
+        <v>61.43462198719289</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>37.73061860787548</v>
+        <v>26.59680068072376</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.4746515329574699</v>
+        <v>0.5356069518832655</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0282263715251699</v>
+        <v>1.656063553111104</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6651</v>
+        <v>6597</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>579.1863984270725</v>
+        <v>686.1324877113778</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>148.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>61.43462194660791</v>
+        <v>52.58978981185699</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>26.59680061446765</v>
+        <v>8.048324780032411</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5356069518832655</v>
+        <v>2.788223532619446</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.656063553454532</v>
+        <v>1.73207997641052</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6753</v>
+        <v>6830</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>576.8024367780479</v>
+        <v>682.888870150818</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>140.5</v>
+        <v>520</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>49.6603378497662</v>
+        <v>63.93761848402227</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>25.69910695210327</v>
+        <v>25.28327662511023</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.4013580407441625</v>
+        <v>0.6594112087358027</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.4327174883505078</v>
+        <v>13.77822858216258</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6805</v>
+        <v>6716</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>560.8140762964887</v>
+        <v>679.3824405282188</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2305</v>
+        <v>124</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>70.30689672965818</v>
+        <v>60.4749561778241</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>29.77933823252026</v>
+        <v>33.78707934641962</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.197836172094355</v>
+        <v>0.6200735099120146</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,84 +1577,84 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>53.08625697684913</v>
+        <v>-0.2769669544383042</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6806</v>
+        <v>6505</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>662.6024384894308</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3.51</v>
+        <v>73.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G22" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>31.69502639099356</v>
+        <v>54.49542812435823</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>32.59319844291417</v>
+        <v>26.69075117360734</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.8214547454404434</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.4112821135359059</v>
+        <v>-0.096735207855404</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6668</v>
+        <v>6741</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>527.4095889967907</v>
+        <v>661.8809477843197</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>44</v>
+        <v>60.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>70.97259462593269</v>
+        <v>65.98738525697428</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>26.79695095239773</v>
+        <v>28.3018194684635</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.712796945948098</v>
+        <v>0.7839136763228849</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.052824725527714</v>
+        <v>0.775289145931978</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6672</v>
+        <v>6613</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>526.2694147139678</v>
+        <v>656.7533031564841</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>275</v>
+        <v>278.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>55.45274281964628</v>
+        <v>51.51029182330496</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>19.64838649897454</v>
+        <v>11.56460659058382</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.7654035218732949</v>
+        <v>4.333368675209359</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.320374429990337</v>
+        <v>3.945235601249028</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6505</v>
+        <v>6672</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>522.6024384894309</v>
+        <v>656.2694147139679</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>73.5</v>
+        <v>275</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>54.49542811311509</v>
+        <v>55.45274282976903</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>26.69075120046801</v>
+        <v>19.64838651714515</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.8214547454404434</v>
+        <v>0.7654035218732949</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.0967352077123111</v>
+        <v>1.320374429856726</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6741</v>
+        <v>6486</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>521.8809477843199</v>
+        <v>644.8790028695697</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>60.8</v>
+        <v>77.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>65.98738518171128</v>
+        <v>63.0628740411823</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>28.30181947227098</v>
+        <v>24.30077497719545</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7839136763228849</v>
+        <v>1.011332131760642</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.7752891461036967</v>
+        <v>0.6736521264183555</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6486</v>
+        <v>6789</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>504.8790028695697</v>
+        <v>639.0891602643718</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>77.8</v>
+        <v>467.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>63.0628740411823</v>
+        <v>55.64202867039587</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>24.30077497307349</v>
+        <v>19.93895919569009</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.011332131760642</v>
+        <v>1.13525524826268</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.6736521263992732</v>
+        <v>6.396443922039541</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6613</v>
+        <v>6770</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>486.7533031564842</v>
+        <v>615.4729726082327</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>278.5</v>
+        <v>73</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>51.51029180168424</v>
+        <v>56.83252256263504</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>11.56460663722529</v>
+        <v>12.80836146535759</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>4.333368675209359</v>
+        <v>0.8855949680694329</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>3.945235601153605</v>
+        <v>0.2995126811072249</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6597</v>
+        <v>6530</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>486.1324877113781</v>
+        <v>608.652223128405</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>52.58978981020265</v>
+        <v>57.79398047119417</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>8.04832475427914</v>
+        <v>14.74674976145824</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.788223532619446</v>
+        <v>0.8778323615703462</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.732079976677628</v>
+        <v>0.8924251979040407</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6830</v>
+        <v>6658</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>482.8888701508184</v>
+        <v>603.5956163509499</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>520</v>
+        <v>171.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>63.9376184709848</v>
+        <v>56.11458167884391</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25.28327653644966</v>
+        <v>12.38769297271301</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6594112087358027</v>
+        <v>1.372936561324669</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>13.7782285825442</v>
+        <v>2.115346827877384</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6770</v>
+        <v>6831</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>470.4729726082329</v>
+        <v>589.6349536784942</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>73</v>
+        <v>618</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>56.83252254527113</v>
+        <v>49.22426665394538</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>12.80836140292897</v>
+        <v>14.80981708999547</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8855949680694329</v>
+        <v>1.02073985040998</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2995126813075595</v>
+        <v>2.700445128425088</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6789</v>
+        <v>6517</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>469.0891602643717</v>
+        <v>583.5781415673439</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>467.5</v>
+        <v>70.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>55.64202867398654</v>
+        <v>57.71123340825213</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>19.9389591758848</v>
+        <v>18.44330713847643</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.13525524826268</v>
+        <v>0.6660834425770552</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>6.396443921371787</v>
+        <v>1.007910053180384</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6768</v>
+        <v>6666</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>467.0290342005642</v>
+        <v>580.4996245241246</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>65</v>
+        <v>44.4</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>39.74311406283971</v>
+        <v>55.65789163825198</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>30.80525417439365</v>
+        <v>18.9994834585253</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.188760359651169</v>
+        <v>0.3652480252165466</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.3149700847510341</v>
+        <v>0.1462973656934504</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6788</v>
+        <v>6771</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>457.4994921134753</v>
+        <v>579.9751171828693</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>361</v>
+        <v>41.75</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>50.80291768003995</v>
+        <v>56.88001454841269</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21.00385583626227</v>
+        <v>37.73061870344699</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.249992240879516</v>
+        <v>0.4746515329574699</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>3.084318293090816</v>
+        <v>0.02822637173504</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6577</v>
+        <v>6533</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>450.0246935411014</v>
+        <v>577.8986910062296</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>80.7</v>
+        <v>261</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>51.5846209692476</v>
+        <v>61.54747181774553</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.85287735305942</v>
+        <v>16.02836053352413</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.434612131928962</v>
+        <v>0.562800226170459</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.033286992829335</v>
+        <v>0.8515646045832987</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6598</v>
+        <v>6753</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>444.4259656408223</v>
+        <v>576.8024367780479</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>28.55</v>
+        <v>140.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>52.85547387694896</v>
+        <v>49.66033786989296</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>22.70553557947345</v>
+        <v>25.69910693437615</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5450926555184642</v>
+        <v>0.4013580407441625</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.0949191511480726</v>
+        <v>-0.4327174884459051</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6605</v>
+        <v>6792</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>440.8550803383258</v>
+        <v>552.6487750693076</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>138.5</v>
+        <v>60</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>51.76431372327456</v>
+        <v>57.05326153922568</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>14.60764545176164</v>
+        <v>14.85264815049699</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5158325127355715</v>
+        <v>0.4628755702375334</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,51 +2425,51 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.0627734085343658</v>
+        <v>0.3232656862262574</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6530</v>
+        <v>6806</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>438.652223128405</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>88.09999999999999</v>
+        <v>3.51</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>57.79398047263091</v>
+        <v>31.69502835174391</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14.74674979902038</v>
+        <v>32.59319844910159</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8778323615703462</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.8924251976750912</v>
+        <v>0.4112821035930523</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6533</v>
+        <v>6526</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>427.8986910062296</v>
+        <v>503.7873717333256</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>261</v>
+        <v>607</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>61.54747174124695</v>
+        <v>52.11534345502924</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>16.02836048598467</v>
+        <v>13.12251736175975</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.562800226170459</v>
+        <v>0.5968193140534362</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.8515646057280506</v>
+        <v>3.513021840457208</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6834</v>
+        <v>6531</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>419.127853997337</v>
+        <v>496.924146568875</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>89.90000000000001</v>
+        <v>927</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,49 +2566,49 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>44.81063058816091</v>
+        <v>55.34912195544086</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>11.06973193469061</v>
+        <v>8.508867949707822</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5150276913727133</v>
+        <v>0.8186850794621255</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.376404914360148</v>
+        <v>8.005110491492832</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6488</v>
+        <v>6834</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>416.1994305506724</v>
+        <v>494.127853997337</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>912</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>43.9748298965367</v>
+        <v>44.81063060557786</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>11.16240255581293</v>
+        <v>11.06973202441558</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.080474119909124</v>
+        <v>0.5150276913727133</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>2.063176819519221</v>
+        <v>-0.3764049144269221</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6517</v>
+        <v>6706</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>413.5781415673439</v>
+        <v>484.0807623849169</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>70.8</v>
+        <v>123</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>57.71123342422569</v>
+        <v>53.23460683613183</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.44330719026038</v>
+        <v>13.84415613800632</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6660834425770552</v>
+        <v>0.5914478701781819</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.007910053065904</v>
+        <v>1.761558747324208</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6582</v>
+        <v>6768</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>401.7357359374931</v>
+        <v>467.0290342005641</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>32.5</v>
+        <v>65</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>55.18023044241343</v>
+        <v>39.74311362815234</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>23.74297893209928</v>
+        <v>30.80525433748284</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.024810600023376</v>
+        <v>2.188760359651169</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.1094588375028259</v>
+        <v>0.3149700851326287</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6581</v>
+        <v>6693</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>393.1256163300348</v>
+        <v>460.2485133049332</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>108.5</v>
+        <v>176.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.93174582282396</v>
+        <v>50.24213383997073</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>23.45448507892985</v>
+        <v>14.29666875802114</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2.053020273016612</v>
+        <v>0.9801767190834252</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.108360407907338</v>
+        <v>1.351610382973282</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6512</v>
+        <v>6788</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>391.3456244718015</v>
+        <v>457.4994921134753</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>20.6</v>
+        <v>361</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>53.48428893288605</v>
+        <v>50.80291774499729</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10.03056101740076</v>
+        <v>21.00385581538515</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6578547429125352</v>
+        <v>1.249992240879516</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,11 +2849,11 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1306395182546865</v>
+        <v>3.084318294235603</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>381.6118522539151</v>
+        <v>456.6118522539152</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>100.5</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>54.38912034626892</v>
+        <v>54.38912046821201</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10.15445715553537</v>
+        <v>10.15445724713491</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.598731606001032</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.210750868417721</v>
+        <v>0.2107508675591612</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6757</v>
+        <v>6568</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>366.0762807801746</v>
+        <v>455.8871792910896</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>56.1</v>
+        <v>129</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.3357027440799</v>
+        <v>41.35779865360841</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>8.234970830530056</v>
+        <v>40.40206352841479</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.244258039695628</v>
+        <v>0.5657658933035614</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0541269526983535</v>
+        <v>1.158549295791804</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6606</v>
+        <v>6577</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>357.3034371625441</v>
+        <v>450.0246935411014</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>25.7</v>
+        <v>80.7</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>43.99433168961752</v>
+        <v>51.5846209692476</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>12.89714851451237</v>
+        <v>22.85287735305942</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6288045866439763</v>
+        <v>1.434612131928962</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0912347090540369</v>
+        <v>-0.0332869929438132</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6708</v>
+        <v>6598</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>355.7551787535023</v>
+        <v>444.4259656408223</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>37.6</v>
+        <v>28.55</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.25938360208164</v>
+        <v>52.85547390827301</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>8.151993631839641</v>
+        <v>22.70553561996788</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.328608427731503</v>
+        <v>0.5450926555184642</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1668370909111338</v>
+        <v>-0.09491915119577291</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6645</v>
+        <v>6605</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>355.7125858553464</v>
+        <v>440.8550803383259</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>12.3</v>
+        <v>138.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>32.91086666921409</v>
+        <v>51.76431394394157</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>27.93441688256746</v>
+        <v>14.60764547758658</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.527469910757516</v>
+        <v>0.5158325127355715</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0319856783000493</v>
+        <v>-0.062773409392943</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6691</v>
+        <v>6642</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>353.7595703636343</v>
+        <v>439.7454644218255</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>615</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>36.4591319786341</v>
+        <v>52.10151678647396</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>22.52362294034528</v>
+        <v>16.71206967045015</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6827143069832392</v>
+        <v>0.3558363998103947</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-7.461889119922532</v>
+        <v>0.0504202418364355</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6515</v>
+        <v>6510</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>350.6273998118125</v>
+        <v>433.3188063529273</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>6285</v>
+        <v>2845</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,49 +3202,49 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>44.51271068651275</v>
+        <v>53.51641660414718</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>16.2690110956262</v>
+        <v>12.5795681242983</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8614044803526889</v>
+        <v>1.945699406656182</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>17.30227504609695</v>
+        <v>11.70839778160547</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6494</v>
+        <v>6781</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>349.7393826634622</v>
+        <v>432.2348097439213</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>53.8</v>
+        <v>1125</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>48.23885376155381</v>
+        <v>55.92865208911028</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>11.6955990070727</v>
+        <v>13.52815022054053</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4889677830891101</v>
+        <v>0.6727860994553948</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.2257299670112472</v>
+        <v>5.30061085480358</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6674</v>
+        <v>6488</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>349.2001384363927</v>
+        <v>416.1994305506724</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>15.8</v>
+        <v>912</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.59193037596906</v>
+        <v>43.97482991433068</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.96603610550348</v>
+        <v>11.16240258857236</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5614765248020466</v>
+        <v>1.080474119909124</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.1230897057642324</v>
+        <v>2.063176818851392</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6658</v>
+        <v>6794</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>348.5956163509498</v>
+        <v>413.8097442198822</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>171.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>56.11458167678781</v>
+        <v>58.24858527757267</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12.38769296269276</v>
+        <v>23.79084642885435</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.372936561324669</v>
+        <v>0.67653220642848</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>2.115346827953681</v>
+        <v>1.027597462655251</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6589</v>
+        <v>6743</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>344.699570622971</v>
+        <v>411.4696574389134</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>48.15</v>
+        <v>27.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46.16856565739659</v>
+        <v>52.84566154012217</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>25.58134667427207</v>
+        <v>22.16813903218262</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.11020188596479</v>
+        <v>0.9185431592121456</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.2483226148028127</v>
+        <v>0.3702613707229433</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6831</v>
+        <v>6582</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>344.6349536784942</v>
+        <v>401.7357359374931</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>618</v>
+        <v>32.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.22426663546145</v>
+        <v>55.18023072413567</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>14.80981713346742</v>
+        <v>23.74297926603447</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.02073985040998</v>
+        <v>1.024810600023376</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>2.700445126898803</v>
+        <v>0.1094588372643331</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6573</v>
+        <v>6698</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>343.1601619494804</v>
+        <v>393.7173305276922</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>17.4</v>
+        <v>32.05</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>47.57254015467134</v>
+        <v>44.94999235264769</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18.47340104695106</v>
+        <v>22.09795027814248</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.110363319990981</v>
+        <v>0.8934547651090825</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.24373562915138</v>
+        <v>0.2992005666956883</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6568</v>
+        <v>6581</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>340.8871792910896</v>
+        <v>393.1256163300348</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>129</v>
+        <v>108.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>41.35779870246254</v>
+        <v>51.93174563301088</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>40.40206352841479</v>
+        <v>23.45448507892985</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5657658933035614</v>
+        <v>2.053020273016612</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>1.15854929598259</v>
+        <v>0.1083604080027488</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6531</v>
+        <v>6512</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>336.924146568875</v>
+        <v>391.3456244718015</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>927</v>
+        <v>20.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>55.34912194572007</v>
+        <v>53.48428893891321</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>8.508867886443868</v>
+        <v>10.0305611623652</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8186850794621255</v>
+        <v>0.6578547429125352</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>8.005110492160643</v>
+        <v>0.1306395181783675</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6796</v>
+        <v>6683</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>336.8045910332373</v>
+        <v>369.247686651842</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>60.6</v>
+        <v>1210</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>51.16276755797468</v>
+        <v>49.07972405766514</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>29.67640603060839</v>
+        <v>17.2724942013291</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.135109648227992</v>
+        <v>0.8815976474568815</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0430706916026427</v>
+        <v>12.88285743815813</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6715</v>
+        <v>6757</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>335.6083697929933</v>
+        <v>366.0762807801746</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>318.5</v>
+        <v>56.1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>38.64463610036247</v>
+        <v>49.33570265994188</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>13.90644055886766</v>
+        <v>8.234970891945892</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7339143630047603</v>
+        <v>1.244258039695628</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-7.754246527778759</v>
+        <v>0.0541269528319145</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6525</v>
+        <v>6606</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>335.2541347019423</v>
+        <v>357.3034371625441</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>139.5</v>
+        <v>25.7</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>47.07880883422311</v>
+        <v>43.99433149413183</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>10.61019915278587</v>
+        <v>12.8971483951742</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5444376801979007</v>
+        <v>0.6288045866439763</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.5380488333471911</v>
+        <v>-0.0912347089491039</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6664</v>
+        <v>6708</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>331.8998369101404</v>
+        <v>355.7551787535023</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>347.5</v>
+        <v>37.6</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.35007766101315</v>
+        <v>51.25938360874616</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.78138597854807</v>
+        <v>8.151993631839641</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.084004173155808</v>
+        <v>1.328608427731503</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>2.282299162884674</v>
+        <v>0.1668370909111338</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6792</v>
+        <v>6645</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>327.6487750693076</v>
+        <v>355.7125858553464</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>60</v>
+        <v>12.3</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>57.05326149885025</v>
+        <v>32.91086657371174</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14.85264813517217</v>
+        <v>27.93441679533853</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4628755702375334</v>
+        <v>2.527469910757516</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.3232656862644153</v>
+        <v>-0.0319856781855741</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6706</v>
+        <v>6691</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>324.0807623849168</v>
+        <v>353.7595703636343</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>123</v>
+        <v>615</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.23460679555164</v>
+        <v>36.45913204540832</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13.84415610546109</v>
+        <v>22.52362293417436</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5914478701781819</v>
+        <v>0.6827143069832392</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>1.761558747515011</v>
+        <v>-7.461889118396293</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6692</v>
+        <v>6515</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>315.6173993236405</v>
+        <v>350.6273998118125</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>24.3</v>
+        <v>6285</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>52.38362417738004</v>
+        <v>44.5127107169638</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9.555027377994987</v>
+        <v>16.26901112810675</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3585819029375407</v>
+        <v>0.8614044803526889</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0879815419966499</v>
+        <v>17.30227502320116</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6655</v>
+        <v>6494</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>311.3389566415387</v>
+        <v>349.7393826634622</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>116</v>
+        <v>53.8</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>47.30184639874806</v>
+        <v>48.23885374388905</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>11.11473867043615</v>
+        <v>11.69559919240513</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7015419119708438</v>
+        <v>0.4889677830891101</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0622341086429745</v>
+        <v>0.2257299670112472</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6719</v>
+        <v>6674</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>301.6784976798215</v>
+        <v>349.2001384363932</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>188</v>
+        <v>15.8</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>34.56761923934151</v>
+        <v>49.59193037596906</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>23.8773565721852</v>
+        <v>24.9660361872983</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8467308699471808</v>
+        <v>0.5614765248020466</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.7374254704694394</v>
+        <v>0.1230897057069932</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6642</v>
+        <v>6589</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>299.7454644218254</v>
+        <v>344.699570622971</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>80.59999999999999</v>
+        <v>48.15</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.1015168056275</v>
+        <v>46.16856561329091</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16.71206961605277</v>
+        <v>25.58134671533834</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3558363998103947</v>
+        <v>1.11020188596479</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0504202418173471</v>
+        <v>-0.2483226147264914</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6794</v>
+        <v>6573</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>298.8097442198822</v>
+        <v>343.1601619494804</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>77.90000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>58.24858527757267</v>
+        <v>47.57254016496962</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>23.79084647152222</v>
+        <v>18.47340102355419</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.67653220642848</v>
+        <v>1.110363319990981</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>1.027597462655251</v>
+        <v>0.2437356291380257</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6510</v>
+        <v>6796</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>293.3188063529273</v>
+        <v>336.8045910332373</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>2845</v>
+        <v>60.6</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,49 +4262,49 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>53.51641659229932</v>
+        <v>51.16276765592462</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12.57956811700211</v>
+        <v>29.6764061096378</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.945699406656182</v>
+        <v>1.135109648227992</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>11.70839777778932</v>
+        <v>0.0430706912782865</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6643</v>
+        <v>6715</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>292.2244729991782</v>
+        <v>335.6083697929933</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>411.5</v>
+        <v>318.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.49233091695456</v>
+        <v>38.64463610710209</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>13.31586789982881</v>
+        <v>13.90644063518769</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2.791344699244549</v>
+        <v>0.7339143630047603</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>1.540115750502222</v>
+        <v>-7.754246528732711</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6693</v>
+        <v>6664</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>290.2485133049332</v>
+        <v>331.8998369101404</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>176.5</v>
+        <v>347.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>50.24213385806025</v>
+        <v>48.35007771109701</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.29666889755643</v>
+        <v>14.78138600169505</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.9801767190834252</v>
+        <v>1.084004173155808</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1.351610382782498</v>
+        <v>2.282299162216873</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6722</v>
+        <v>6525</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>288.9445767781365</v>
+        <v>325.2541347019423</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>32.7</v>
+        <v>139.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.42195355774251</v>
+        <v>47.07880883068507</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>32.711588705809</v>
+        <v>10.61019911288535</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.0412864367983582</v>
+        <v>0.5444376801979007</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1324246337471341</v>
+        <v>0.538048833576168</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6680</v>
+        <v>6579</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>284.5801120855387</v>
+        <v>321.1950794459394</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>52</v>
+        <v>146.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>51.72540706045484</v>
+        <v>39.82248602141777</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7.527748385946985</v>
+        <v>14.97471955731048</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.9354973724596568</v>
+        <v>0.4693836809289511</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>2.369721051907304</v>
+        <v>-0.778314425471955</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6695</v>
+        <v>6692</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>283.5425645077504</v>
+        <v>315.6173993236407</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>48.6</v>
+        <v>24.3</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45.48594848447211</v>
+        <v>52.38362419631888</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15.36311422275513</v>
+        <v>9.555027385447694</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.9565454967590652</v>
+        <v>0.3585819029375407</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1954816391093001</v>
+        <v>0.0879815420061927</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6498</v>
+        <v>6655</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>281.1783427249731</v>
+        <v>311.3389566415386</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>116</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>44.43896804776286</v>
+        <v>47.30184187342142</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>21.40032650562898</v>
+        <v>11.11473951668161</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5784033309271813</v>
+        <v>0.7015419119708438</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.6575333059409298</v>
+        <v>0.062234132110701</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6526</v>
+        <v>6719</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>278.7873717333256</v>
+        <v>301.6784976798215</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>607</v>
+        <v>188</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>52.11534333367244</v>
+        <v>34.56761932998019</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>13.1225173400925</v>
+        <v>23.87735659306071</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5968193140534362</v>
+        <v>0.8467308699471808</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>3.51302184179276</v>
+        <v>0.7374254699924361</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6679</v>
+        <v>6643</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>274.0109361105307</v>
+        <v>292.2244729991781</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>200.5</v>
+        <v>411.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>40.57517012948043</v>
+        <v>44.49233096506003</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>23.2081431558241</v>
+        <v>13.3158679564261</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.828521369349789</v>
+        <v>2.791344699244549</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.617505401677889</v>
+        <v>1.54011574935746</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6534</v>
+        <v>6722</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>273.6019115398304</v>
+        <v>288.9445767781365</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>92</v>
+        <v>32.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46.1838525249601</v>
+        <v>43.42195397359878</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>14.46135180710114</v>
+        <v>32.71158870164259</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4316609763089994</v>
+        <v>0.0412864367983582</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1828126069119887</v>
+        <v>0.1324246333655443</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6548</v>
+        <v>6680</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>272.7863993535585</v>
+        <v>284.5801120855387</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>52</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>47.2059364477016</v>
+        <v>51.72540706469829</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>12.08954898148442</v>
+        <v>7.527748385946989</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.8482505777902438</v>
+        <v>0.9354973724596568</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.3250256872090959</v>
+        <v>2.369721051869143</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6541</v>
+        <v>6695</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>252.6055158624361</v>
+        <v>283.5425645077504</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>34</v>
+        <v>48.6</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>32.18957176017435</v>
+        <v>45.48594854122722</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>13.73964734088998</v>
+        <v>15.36311423522857</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>3.616948679706864</v>
+        <v>0.9565454967590652</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.1488005580714098</v>
+        <v>0.1954816390997562</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6807</v>
+        <v>6498</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>252.4336382623606</v>
+        <v>281.1783427249731</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>32.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>31.48181180377073</v>
+        <v>44.43896821773939</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>23.88975976517229</v>
+        <v>21.40032647896504</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6950816025801428</v>
+        <v>0.5784033309271813</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.6441799296372641</v>
+        <v>0.6575333054639447</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6657</v>
+        <v>6679</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>250.4774214914501</v>
+        <v>274.0109361105307</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>29.9</v>
+        <v>200.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>40.9277519186717</v>
+        <v>40.57517025196089</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>25.50521460169218</v>
+        <v>23.20814317324602</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.015331366784568</v>
+        <v>0.828521369349789</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.1714679978941393</v>
+        <v>1.61750540148711</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6625</v>
+        <v>6534</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>248.3631643537957</v>
+        <v>273.6019115398304</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>76.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>47.79173323533034</v>
+        <v>46.18384622326293</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>9.341071954435902</v>
+        <v>14.46135073248269</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6936241952206904</v>
+        <v>0.4316609763089994</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0039313447715235</v>
+        <v>-0.1828125920300209</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6641</v>
+        <v>6548</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>247.9820108017805</v>
+        <v>272.7863993535585</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>17.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>37.51902289989141</v>
+        <v>47.20593645136226</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>8.185096162412609</v>
+        <v>12.08954904692381</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3671658783787027</v>
+        <v>0.8482505777902438</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0391651314275974</v>
+        <v>0.3250256871327778</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6579</v>
+        <v>6560</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>246.1950794459394</v>
+        <v>268.6012912481606</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>146.5</v>
+        <v>31</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>39.82248601175769</v>
+        <v>50.40058035544868</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.97471957474652</v>
+        <v>19.95687261301111</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4693836809289511</v>
+        <v>0.5723771301296463</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.7783144255673502</v>
+        <v>0.4539589266067301</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6803</v>
+        <v>6485</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>242.7328826341626</v>
+        <v>266.9002135499005</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>270.5</v>
+        <v>62.3</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>48.49326376269537</v>
+        <v>46.66903340686789</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>21.59725778210446</v>
+        <v>18.86722738077725</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.8502043187471761</v>
+        <v>0.8209194636127357</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.5338029028479687</v>
+        <v>0.7458372770429817</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6552</v>
+        <v>6541</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>241.4727950436876</v>
+        <v>252.6055158624353</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>24.7</v>
+        <v>34</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.3645875040443</v>
+        <v>32.18957200165168</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12.38371701016697</v>
+        <v>13.73964735969538</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.037374157930705</v>
+        <v>3.616948679706864</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1908480089648407</v>
+        <v>-0.1488005581286513</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6743</v>
+        <v>6807</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>241.4696574389134</v>
+        <v>252.4336382623606</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>27.6</v>
+        <v>32.8</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>52.84566149789752</v>
+        <v>31.48181199111412</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>22.16813893465592</v>
+        <v>23.88975966477201</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.9185431592121456</v>
+        <v>0.6950816025801428</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.37026137078018</v>
+        <v>-0.6441799299043791</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6689</v>
+        <v>6657</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>233.7279676562102</v>
+        <v>250.4774214914502</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>61.8</v>
+        <v>29.9</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>50.01304105194112</v>
+        <v>40.92775226314931</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.33487834974696</v>
+        <v>25.50521455205939</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.9107034223634189</v>
+        <v>1.015331366784568</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,11 +5340,11 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.1425216676323931</v>
+        <v>0.1714679971500402</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>228.562189889643</v>
+        <v>248.562189889643</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>43.9</v>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.13094677617728</v>
+        <v>45.13094688167818</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>15.69260551574799</v>
+        <v>15.69260555993776</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.7660015849276132</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6570</v>
+        <v>6625</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>228.276402681329</v>
+        <v>248.3631643537949</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>50.4</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>37.32531690624954</v>
+        <v>47.79173367535289</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>13.90371134856606</v>
+        <v>9.341071871380208</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.535676894552958</v>
+        <v>0.6936241952206904</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.6263222597451108</v>
+        <v>0.0039313441991447</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6585</v>
+        <v>6641</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>226.6409467906732</v>
+        <v>247.9820108017805</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>112.5</v>
+        <v>17.4</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.61627955200981</v>
+        <v>37.51902302190999</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.26880692122552</v>
+        <v>8.185096132258838</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.2539655986582336</v>
+        <v>0.3671658783787027</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.09320887216552989</v>
+        <v>-0.0391651314275974</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6720</v>
+        <v>6803</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>226.2648175772514</v>
+        <v>242.7328826341626</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>132.5</v>
+        <v>270.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>41.65818927617472</v>
+        <v>48.49326364844215</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>27.01475468067995</v>
+        <v>21.59725775238026</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.451920103200497</v>
+        <v>0.8502043187471761</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.237718989451249</v>
+        <v>0.5338029033249876</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6558</v>
+        <v>6552</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>216.9022211839601</v>
+        <v>241.4727950436876</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>24.65</v>
+        <v>24.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>41.40005821562071</v>
+        <v>43.36458748252801</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>27.08637743119108</v>
+        <v>12.38371707544496</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.037797159711959</v>
+        <v>1.037374157930705</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1112680914011099</v>
+        <v>0.1908480090220798</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6823</v>
+        <v>6689</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>216.7019222733456</v>
+        <v>233.7279676562173</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>62.2</v>
+        <v>61.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>44.44311848730421</v>
+        <v>50.01304108748116</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.81801272951083</v>
+        <v>15.33487847593323</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.458554520969043</v>
+        <v>0.9107034223634189</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0646525603604497</v>
+        <v>0.142521667460687</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6546</v>
+        <v>6570</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>214.7186578650951</v>
+        <v>228.2764026813291</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>62.9</v>
+        <v>50.4</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>50.60165299896829</v>
+        <v>37.32531691249176</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17.62687241031448</v>
+        <v>13.90371133542815</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3549728183795753</v>
+        <v>0.535676894552958</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.3308259234495983</v>
+        <v>-0.6263222598023437</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6799</v>
+        <v>6585</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>214.4714039159485</v>
+        <v>226.6409467906732</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>81</v>
+        <v>112.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>45.97762289411688</v>
+        <v>42.61627955019031</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15.06322986431104</v>
+        <v>17.26880693817411</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4298478796950199</v>
+        <v>0.2539655986582336</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.3087099869502077</v>
+        <v>-0.0932088724898672</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6725</v>
+        <v>6720</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>213.1132953875451</v>
+        <v>226.2648175772507</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>222</v>
+        <v>132.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>35.07906508720494</v>
+        <v>41.65818929887761</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>30.29530859577212</v>
+        <v>27.01475466507595</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.9870512746401524</v>
+        <v>0.451920103200497</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>1.851944357356121</v>
+        <v>-0.2377189904052197</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6550</v>
+        <v>6558</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>211.2593485650327</v>
+        <v>216.9022211839604</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>10.7</v>
+        <v>24.65</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>42.69959892799447</v>
+        <v>41.40005849833872</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>26.88817569649761</v>
+        <v>27.0863774578878</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.471892044365873</v>
+        <v>1.037797159711959</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.07507271107128249</v>
+        <v>0.1112680911816961</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5880,21 +5880,21 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6811</v>
+        <v>6823</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>207.9743015516985</v>
+        <v>216.7019222733473</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>223.5</v>
+        <v>62.2</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>46.18949126624865</v>
+        <v>44.4431185610208</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>9.868217327918581</v>
+        <v>17.81801273449717</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5147157766924969</v>
+        <v>1.458554520969043</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.6833818315675896</v>
+        <v>0.06465256032228819</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6690</v>
+        <v>6546</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>207.7590016851739</v>
+        <v>214.7186578650951</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>164.5</v>
+        <v>62.9</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.99745935010024</v>
+        <v>50.60165300746543</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>10.46148805843998</v>
+        <v>17.62687241947703</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5141181972415901</v>
+        <v>0.3549728183795753</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.2288809480328018</v>
+        <v>0.3308259233541962</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6592</v>
+        <v>6799</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>206.1092591340025</v>
+        <v>214.4714039159485</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>60.2</v>
+        <v>81</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>43.99584368620692</v>
+        <v>45.97762295257938</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>10.83724092986401</v>
+        <v>15.06322983319264</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.777501412592719</v>
+        <v>0.4298478796950199</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.011756471571966</v>
+        <v>0.3087099867403426</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6671</v>
+        <v>6725</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>202.6849574231885</v>
+        <v>213.1132953875453</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>23</v>
+        <v>222</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>47.3220665523229</v>
+        <v>35.07906512187516</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>19.63671144117442</v>
+        <v>30.29530860259381</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.1043086710455653</v>
+        <v>0.9870512746401524</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1157109499229004</v>
+        <v>1.85194435754692</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6683</v>
+        <v>6550</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>199.247686651842</v>
+        <v>211.2593485650327</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>1210</v>
+        <v>10.7</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>49.0797240273058</v>
+        <v>42.69959911538353</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>17.27249413465925</v>
+        <v>26.88817568985398</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8815976474568815</v>
+        <v>1.471892044365873</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>12.88285743930322</v>
+        <v>0.0750727108423285</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6667</v>
+        <v>6811</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>191.1530857666984</v>
+        <v>207.9743015516985</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>217.5</v>
+        <v>223.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>38.17206930542238</v>
+        <v>46.18949136319359</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>29.99590148433098</v>
+        <v>9.868217339758251</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.407995688066571</v>
+        <v>0.5147157766924969</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.684067891399577</v>
+        <v>-0.6833818323307759</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6781</v>
+        <v>6690</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>182.2348097439213</v>
+        <v>207.7590016851739</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>1125</v>
+        <v>164.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>55.92865208180339</v>
+        <v>50.99745937068887</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.52815020664328</v>
+        <v>10.46148808918559</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.6727860994553948</v>
+        <v>0.5141181972415901</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>5.30061085480358</v>
+        <v>0.2288809483189974</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6821</v>
+        <v>6592</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>180.9339270540818</v>
+        <v>206.1092591340025</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>41.55</v>
+        <v>60.2</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.12066716243772</v>
+        <v>43.99584372149049</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.34396539153636</v>
+        <v>10.8372409033677</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5949074607480649</v>
+        <v>1.777501412592719</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.5278750649472348</v>
+        <v>-0.0117564716292032</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6624</v>
+        <v>6671</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>180.8468731286068</v>
+        <v>202.6849574231885</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>30.91937798576092</v>
+        <v>47.3220666382579</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>8.218504446143601</v>
+        <v>19.63671142094072</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>3.198533792109697e-05</v>
+        <v>0.1043086710455653</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-2.623479187229112</v>
+        <v>0.115710949846585</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6776</v>
+        <v>6667</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>175.5293984663425</v>
+        <v>191.153085766698</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>53</v>
+        <v>217.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>41.27863497826618</v>
+        <v>38.17206926579482</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15.82354531364089</v>
+        <v>29.99590149411933</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.6577945156388681</v>
+        <v>1.407995688066571</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.013948763357418</v>
+        <v>0.6840678915903737</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6591</v>
+        <v>6821</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>172.8554765163838</v>
+        <v>180.9339270540818</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>42.7</v>
+        <v>41.55</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>37.72929422832043</v>
+        <v>43.12066714815872</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>30.06030323161401</v>
+        <v>17.34396538932455</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.7139826361407053</v>
+        <v>0.5949074607480649</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.1066052622767015</v>
+        <v>0.5278750650044741</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6754</v>
+        <v>6624</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>172.6981307012556</v>
+        <v>180.8468731286068</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>42.1</v>
+        <v>0</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>48.48603214825227</v>
+        <v>30.91937797950239</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.82700811358888</v>
+        <v>8.21850443579606</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.9676436775962191</v>
+        <v>3.198533792109697e-05</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0686018415743281</v>
+        <v>-2.623479187162335</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6698</v>
+        <v>6776</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>168.7173305276922</v>
+        <v>175.5293984663425</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>32.05</v>
+        <v>53</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.94999225921809</v>
+        <v>41.27863525826162</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>22.09795022445444</v>
+        <v>15.8235452108514</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.8934547651090825</v>
+        <v>0.6577945156388681</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.2992005668483271</v>
+        <v>0.0139487631284637</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6561</v>
+        <v>6591</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>161.5270069328942</v>
+        <v>172.8554765163856</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>321</v>
+        <v>42.7</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>45.32739671230225</v>
+        <v>37.7292943935717</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>9.663385353031044</v>
+        <v>30.0603033056103</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.8775968914651792</v>
+        <v>0.7139826361407053</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.2512338876749695</v>
+        <v>0.106605262295788</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6735</v>
+        <v>6754</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>158.9943251501634</v>
+        <v>172.6981307012556</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>63.8</v>
+        <v>42.1</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>44.29467534437626</v>
+        <v>48.48603226400002</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16.23918502596238</v>
+        <v>13.82700807410534</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.8442015893505227</v>
+        <v>0.9676436775962191</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.7570463129370557</v>
+        <v>0.0686018414407744</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6614</v>
+        <v>6561</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>154.6087575308517</v>
+        <v>161.5270069328942</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>35.9</v>
+        <v>321</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>39.04079943809308</v>
+        <v>45.32739681670304</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>8.854529032145392</v>
+        <v>9.663385377750114</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6056766459532442</v>
+        <v>0.8775968914651792</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.1340513153918452</v>
+        <v>0.2512338865301959</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6485</v>
+        <v>6735</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>151.9002135499005</v>
+        <v>158.9943251501634</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>62.3</v>
+        <v>63.8</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>46.66903339541674</v>
+        <v>44.29467539366712</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>18.86722740944322</v>
+        <v>16.23918502647536</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.8209194636127357</v>
+        <v>0.8442015893505227</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.7458372770811388</v>
+        <v>0.7570463128416431</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6732</v>
+        <v>6614</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>150.95185201948</v>
+        <v>154.6087575308517</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>151.5</v>
+        <v>35.9</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>41.02288423587609</v>
+        <v>39.0407997480021</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>18.16497716688239</v>
+        <v>8.854529032145393</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.7831967573348793</v>
+        <v>0.6056766459532442</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.9059349832176542</v>
+        <v>0.1340513154872373</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6684</v>
+        <v>6732</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>149.0532581602593</v>
+        <v>150.95185201948</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>46.55</v>
+        <v>151.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>42.85798438718682</v>
+        <v>41.02288421461677</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>11.37624187078563</v>
+        <v>18.16497719126913</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.4335779043734621</v>
+        <v>0.7831967573348793</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.1297253214221756</v>
+        <v>0.9059349826452374</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6763</v>
+        <v>6684</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>147.1439969595277</v>
+        <v>149.0532581602593</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>41.55</v>
+        <v>46.55</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>40.97557738509224</v>
+        <v>42.85798439831422</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>19.745557522095</v>
+        <v>11.37624188627128</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.7733371900000814</v>
+        <v>0.4335779043734621</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0495213886608094</v>
+        <v>0.129725321250465</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6556</v>
+        <v>6763</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>144.6399984144713</v>
+        <v>147.1439969595277</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>60.5</v>
+        <v>41.55</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>42.32119108374613</v>
+        <v>40.97557734161316</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17.01166233554088</v>
+        <v>19.745557522095</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.3482179434657927</v>
+        <v>0.7733371900000814</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.4104151807768923</v>
+        <v>0.0495213885844901</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6504</v>
+        <v>6556</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>139.7564426864143</v>
+        <v>144.6399984144713</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>37.4</v>
+        <v>60.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>44.56675101966197</v>
+        <v>42.32119592080197</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.8430125382194</v>
+        <v>17.01166233554088</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.348215836262146</v>
+        <v>0.3482179434657927</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.1012995739493241</v>
+        <v>0.4104151807768923</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6835</v>
+        <v>6504</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>127.3729536450215</v>
+        <v>139.7564426864143</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>31</v>
+        <v>37.4</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>44.08862646432023</v>
+        <v>44.56675098611564</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>17.37542072616144</v>
+        <v>15.84301255735495</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.8535078622359614</v>
+        <v>0.348215836262146</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.1405040556859623</v>
+        <v>-0.1012995739874845</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6790</v>
+        <v>6835</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>116.255342968317</v>
+        <v>127.3729536450215</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>37.95</v>
+        <v>31</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>41.57206070986798</v>
+        <v>44.08862646432023</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>13.15774240187252</v>
+        <v>17.37542071757365</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.108432800662498</v>
+        <v>0.8535078622359614</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0452366754533277</v>
+        <v>0.14050405566688</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>6838</v>
+        <v>6790</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>116.1462641965909</v>
+        <v>116.255342968317</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>23</v>
+        <v>37.95</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>44.55104680653817</v>
+        <v>41.57206068374449</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>11.6695283686592</v>
+        <v>13.15774238469403</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.7251472034117226</v>
+        <v>1.108432800662498</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.0526371894591965</v>
+        <v>0.0452366754628676</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>6560</v>
+        <v>6838</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>68.60129124816054</v>
+        <v>116.1462641965909</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,16 +7230,16 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>50.40058033267854</v>
+        <v>44.55104720454306</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>19.95687261301111</v>
+        <v>11.66952842928432</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5723771301296463</v>
+        <v>0.7251472034117226</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L128" s="2" t="n">
         <v>0</v>
@@ -7248,11 +7248,11 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.4539589269024606</v>
+        <v>0.0526371891062261</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
